--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,7 +88,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Allowed coded values for SpecificFinding, generated from enum_models.py.</t>
+    <t>Allowed coded values for SpecificFinding</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="65">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -170,6 +170,12 @@
   </si>
   <si>
     <t>Hemorrhagic cerebral infarction (disorder)</t>
+  </si>
+  <si>
+    <t>49436004</t>
+  </si>
+  <si>
+    <t>Atrial fibrillation (disorder)</t>
   </si>
   <si>
     <t>http://snomed.info/sct</t>
@@ -515,7 +521,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -604,18 +610,26 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>30</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B12" t="s" s="2">
-        <v>51</v>
+      <c r="B13" t="s" s="2">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -642,18 +656,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
@@ -669,7 +683,7 @@
         <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -696,10 +710,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -715,7 +729,7 @@
         <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -742,10 +756,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
@@ -761,7 +775,7 @@
         <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T11:21:15+00:00</t>
+    <t>2026-06-11T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,7 +88,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Allowed coded values for SpecificFinding</t>
+    <t>Allowed coded values for specific stroke-related findings.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -172,12 +172,6 @@
     <t>Hemorrhagic cerebral infarction (disorder)</t>
   </si>
   <si>
-    <t>49436004</t>
-  </si>
-  <si>
-    <t>Atrial fibrillation (disorder)</t>
-  </si>
-  <si>
     <t>http://snomed.info/sct</t>
   </si>
   <si>
@@ -209,6 +203,12 @@
   </si>
   <si>
     <t>No Finding</t>
+  </si>
+  <si>
+    <t>atrial-fibrillation-flutter</t>
+  </si>
+  <si>
+    <t>Atrial fibrillation/flutter</t>
   </si>
   <si>
     <t>http://tecnomod-um.org/CodeSystem/specific-finding-cs</t>
@@ -521,7 +521,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -610,26 +610,18 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>52</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -656,18 +648,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -683,7 +675,7 @@
         <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -710,10 +702,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -729,7 +721,7 @@
         <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -739,7 +731,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -756,25 +748,33 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B4" t="s" s="2">
+      <c r="B5" t="s" s="2">
         <v>64</v>
       </c>
     </row>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -28,7 +28,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/specific-finding-vs</t>
+    <t>http://qualityregistry.org/ValueSet/specific-finding-vs</t>
   </si>
   <si>
     <t>Version</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -76,7 +76,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -115,7 +115,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/CodeSystem/mtici-code-cs</t>
+    <t>http://qualityregistry.org/CodeSystem/mtici-code-cs</t>
   </si>
   <si>
     <t>371863001</t>
@@ -187,7 +187,7 @@
     <t>Hypoperfusion Volume</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/CodeSystem/perfusion-volume-cs</t>
+    <t>http://qualityregistry.org/CodeSystem/perfusion-volume-cs</t>
   </si>
   <si>
     <t>old-infarct</t>
@@ -196,7 +196,7 @@
     <t>Old Infarct</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/CodeSystem/old-infarct-cs</t>
+    <t>http://qualityregistry.org/CodeSystem/old-infarct-cs</t>
   </si>
   <si>
     <t>no-finding</t>
@@ -211,7 +211,7 @@
     <t>Atrial fibrillation/flutter</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/CodeSystem/specific-finding-cs</t>
+    <t>http://qualityregistry.org/CodeSystem/specific-finding-cs</t>
   </si>
 </sst>
 </file>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-specific-finding-vs.xlsx
+++ b/ValueSet-specific-finding-vs.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
